--- a/resources/templates/system/sales_invoice.xlsx
+++ b/resources/templates/system/sales_invoice.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Invoice" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A$1:$F$70</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
   <si>
     <r>
       <t xml:space="preserve">PROFORMA INVOICE</t>
@@ -218,37 +218,32 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve"> BALANCE MONEY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TOTAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SUB TOTAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TAX D/C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AUTO LODING</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">COMMISSION</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AUTO LODING</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TAX D/C</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SUB TOTAL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> DEPOSIT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TOTAL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> BALANCE MONEY</t>
     </r>
   </si>
 </sst>
@@ -390,7 +385,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -457,9 +452,6 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
   </fills>
   <borders count="39">
     <border>
@@ -1194,7 +1186,7 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="35" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="12" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
     </xf>
   </cellXfs>
@@ -1272,13 +1264,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1981200</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>1247775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1633,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13.625" customWidth="true" style="30"/>
@@ -2064,410 +2056,679 @@
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
     </row>
-    <row r="19" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62"/>
+    <row r="19" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="60"/>
       <c r="G19" s="41"/>
       <c r="H19" s="41"/>
     </row>
-    <row r="20" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
+    <row r="20" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="41"/>
     </row>
-    <row r="21" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
+    <row r="21" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="41"/>
     </row>
-    <row r="22" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
+    <row r="22" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="41"/>
     </row>
-    <row r="23" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
+    <row r="23" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="41"/>
     </row>
-    <row r="24" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="63" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">COMMISSION</t>
-          </r>
-        </is>
-      </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="64">
-        <v>200</v>
-      </c>
-      <c r="F24" s="54"/>
+    <row r="24" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="60"/>
       <c r="G24" s="41"/>
       <c r="H24" s="41"/>
     </row>
-    <row r="25" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="63" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">AUTO LODING</t>
-          </r>
-        </is>
-      </c>
-      <c r="D25" s="52"/>
-      <c r="E25" s="64" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="F25" s="54"/>
+    <row r="25" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="60"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
     </row>
-    <row r="26" spans="1:8" customHeight="1" ht="24.75" s="41" customFormat="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="65" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">TAX D/C</t>
-          </r>
-        </is>
-      </c>
-      <c r="D26" s="55"/>
-      <c r="E26" s="64">
-        <v>-270</v>
-      </c>
-      <c r="F26" s="54"/>
+    <row r="26" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="60"/>
       <c r="G26" s="41"/>
       <c r="H26" s="41"/>
     </row>
-    <row r="27" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="66" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SUB TOTAL</t>
-          </r>
-        </is>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="67" t="str">
-        <f>SUM(E18:F26)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="68"/>
+    <row r="27" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="60"/>
       <c r="G27" s="41"/>
       <c r="H27" s="41"/>
     </row>
-    <row r="28" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="69" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> DEPOSIT</t>
-          </r>
-        </is>
-      </c>
-      <c r="D28" s="70"/>
-      <c r="E28" s="71" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="F28" s="72"/>
+    <row r="28" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="60"/>
       <c r="G28" s="41"/>
       <c r="H28" s="41"/>
     </row>
-    <row r="29" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="73" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> DEPOSIT</t>
-          </r>
-        </is>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="64">
-        <v>300</v>
-      </c>
-      <c r="F29" s="54"/>
+    <row r="29" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="60"/>
       <c r="G29" s="41"/>
       <c r="H29" s="41"/>
     </row>
-    <row r="30" spans="1:8" customHeight="1" ht="24.75" s="41" customFormat="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="64" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="F30" s="54"/>
+    <row r="30" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60"/>
       <c r="G30" s="41"/>
       <c r="H30" s="41"/>
     </row>
-    <row r="31" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="66" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">TOTAL</t>
-          </r>
-        </is>
-      </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="67" t="str">
-        <f>SUM(E27:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="68"/>
+    <row r="31" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60"/>
       <c r="G31" s="41"/>
       <c r="H31" s="41"/>
     </row>
-    <row r="32" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="74" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="64" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="F32" s="54"/>
+    <row r="32" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A32" s="19"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60"/>
       <c r="G32" s="41"/>
       <c r="H32" s="41"/>
     </row>
-    <row r="33" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="74" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="64" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="F33" s="54"/>
+    <row r="33" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="60"/>
       <c r="G33" s="41"/>
       <c r="H33" s="41"/>
     </row>
-    <row r="34" spans="1:8" customHeight="1" ht="37.5" s="41" customFormat="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="75" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> BALANCE MONEY</t>
-          </r>
-        </is>
-      </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="76" t="str">
-        <f>SUM(E27:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="77"/>
+    <row r="34" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="60"/>
       <c r="G34" s="41"/>
       <c r="H34" s="41"/>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="29"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="29"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="29"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-    </row>
-    <row r="40" spans="1:8" customHeight="1" ht="106.5" s="41" customFormat="1">
-      <c r="A40" s="29"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="10"/>
+    <row r="35" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+    </row>
+    <row r="36" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A36" s="19"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+    </row>
+    <row r="37" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+    </row>
+    <row r="38" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A38" s="19"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+    </row>
+    <row r="39" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A39" s="19"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+    </row>
+    <row r="40" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="60"/>
       <c r="G40" s="41"/>
       <c r="H40" s="41"/>
     </row>
-    <row r="41" spans="1:8" customHeight="1" ht="13.5" s="41" customFormat="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="12"/>
+    <row r="41" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="60"/>
       <c r="G41" s="41"/>
       <c r="H41" s="41"/>
     </row>
+    <row r="42" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+    </row>
+    <row r="43" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+    </row>
+    <row r="44" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A44" s="19"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+    </row>
+    <row r="45" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+    </row>
+    <row r="46" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+    </row>
+    <row r="47" spans="1:8" customHeight="1" ht="21.75">
+      <c r="A47" s="19"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+    </row>
+    <row r="48" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A48" s="4"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+    </row>
+    <row r="49" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A49" s="4"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="30" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H49" s="41"/>
+    </row>
+    <row r="50" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H50" s="41"/>
+    </row>
+    <row r="51" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A51" s="4"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="61"/>
+      <c r="F51" s="62"/>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H51" s="41"/>
+    </row>
+    <row r="52" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A52" s="4"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="62"/>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H52" s="41"/>
+    </row>
+    <row r="53" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A53" s="4"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="63" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">COMMISSION</t>
+          </r>
+        </is>
+      </c>
+      <c r="D53" s="52"/>
+      <c r="E53" s="64">
+        <v>200</v>
+      </c>
+      <c r="F53" s="54"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+    </row>
+    <row r="54" spans="1:8" customHeight="1" ht="21.75" s="41" customFormat="1">
+      <c r="A54" s="4"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="63" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">AUTO LODING</t>
+          </r>
+        </is>
+      </c>
+      <c r="D54" s="52"/>
+      <c r="E54" s="64" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="F54" s="54"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+    </row>
+    <row r="55" spans="1:8" customHeight="1" ht="24.75" s="41" customFormat="1">
+      <c r="A55" s="4"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="65" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">TAX D/C</t>
+          </r>
+        </is>
+      </c>
+      <c r="D55" s="55"/>
+      <c r="E55" s="64">
+        <v>-270</v>
+      </c>
+      <c r="F55" s="54"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+    </row>
+    <row r="56" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A56" s="4"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="66" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">SUB TOTAL</t>
+          </r>
+        </is>
+      </c>
+      <c r="D56" s="50"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+    </row>
+    <row r="57" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="71" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="F57" s="72"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+    </row>
+    <row r="58" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A58" s="4"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="64">
+        <v>300</v>
+      </c>
+      <c r="F58" s="54"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+    </row>
+    <row r="59" spans="1:8" customHeight="1" ht="24.75" s="41" customFormat="1">
+      <c r="A59" s="4"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="64" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="F59" s="54"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+    </row>
+    <row r="60" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A60" s="4"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="66" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">TOTAL</t>
+          </r>
+        </is>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+    </row>
+    <row r="61" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A61" s="4"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="74" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="D61" s="52"/>
+      <c r="E61" s="64" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="F61" s="54"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+    </row>
+    <row r="62" spans="1:8" customHeight="1" ht="22.5" s="41" customFormat="1">
+      <c r="A62" s="4"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="74" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="D62" s="52"/>
+      <c r="E62" s="64" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="F62" s="54"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+    </row>
+    <row r="63" spans="1:8" customHeight="1" ht="37.5" s="41" customFormat="1">
+      <c r="A63" s="4"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="75" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> BALANCE MONEY</t>
+          </r>
+        </is>
+      </c>
+      <c r="D63" s="50"/>
+      <c r="E63" s="76"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="29"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="29"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="29"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="29"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="29"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+    </row>
+    <row r="69" spans="1:8" customHeight="1" ht="106.5" s="41" customFormat="1">
+      <c r="A69" s="29"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+    </row>
+    <row r="70" spans="1:8" customHeight="1" ht="13.5" s="41" customFormat="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+    </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C53:D53"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C55:D55"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C58:D58"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E57:F57"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C60:D60"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E63:F63"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E59:F59"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C56:D56"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E56:F56"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E55:F55"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="A2:C3"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E54:F54"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C57:D57"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E11:F11"/>
